--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,32 +793,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844714</v>
+        <v>129844718</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>92059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528824</v>
+        <v>528800</v>
       </c>
       <c r="R3" t="n">
-        <v>6627711</v>
+        <v>6627621</v>
       </c>
       <c r="S3" t="n">
         <v>26</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,32 +911,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844718</v>
+        <v>129844714</v>
       </c>
       <c r="B4" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528800</v>
+        <v>528824</v>
       </c>
       <c r="R4" t="n">
-        <v>6627621</v>
+        <v>6627711</v>
       </c>
       <c r="S4" t="n">
         <v>26</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,32 +793,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129844718</v>
+        <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>92059</v>
+        <v>91623</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528800</v>
+        <v>528824</v>
       </c>
       <c r="R3" t="n">
-        <v>6627621</v>
+        <v>6627711</v>
       </c>
       <c r="S3" t="n">
         <v>26</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,32 +911,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129844714</v>
+        <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528824</v>
+        <v>528800</v>
       </c>
       <c r="R4" t="n">
-        <v>6627711</v>
+        <v>6627621</v>
       </c>
       <c r="S4" t="n">
         <v>26</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 19656-2025 artfynd.xlsx
+++ b/artfynd/A 19656-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129844713</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129844714</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,11 +914,11 @@
         <v>129844718</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1026,6 +1026,124 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129844721</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92564</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röda jorden, Riddarhyttan , Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528841</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6627526</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
